--- a/files/MAP - コピー/MAP002.xlsx
+++ b/files/MAP - コピー/MAP002.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\MAP - コピー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F89DD1-C462-493F-A981-B0731BC04602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9E39FE-A63D-44F0-88D7-AD487B1D10EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="585" windowWidth="26205" windowHeight="14850" activeTab="1" xr2:uid="{38351AC5-F874-4B4A-BA41-290077078325}"/>
+    <workbookView xWindow="2595" yWindow="585" windowWidth="26205" windowHeight="14850" activeTab="2" xr2:uid="{38351AC5-F874-4B4A-BA41-290077078325}"/>
   </bookViews>
   <sheets>
     <sheet name="MAP" sheetId="3" r:id="rId1"/>
     <sheet name="MAP_ELV" sheetId="6" r:id="rId2"/>
-    <sheet name="visual" sheetId="5" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId3"/>
+    <sheet name="visual" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="152">
   <si>
     <t>##このページは人間が確認するための疑似ヘクスマップ</t>
     <rPh sb="8" eb="10">
@@ -641,6 +642,228 @@
   </si>
   <si>
     <t>090-9863-4829</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>種類</t>
+    <rPh sb="0" eb="2">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現敵</t>
+    <rPh sb="0" eb="2">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生命力</t>
+    <rPh sb="0" eb="3">
+      <t>セイメイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動速度</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動距離(m)</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動間隔(秒)</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃射程(m)</t>
+    <rPh sb="0" eb="4">
+      <t>コウゲキシャテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃頻度</t>
+    <rPh sb="0" eb="4">
+      <t>コウゲキヒンド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重量</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デバフ抵抗</t>
+    <rPh sb="3" eb="5">
+      <t>テイコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大きさ</t>
+    <rPh sb="0" eb="1">
+      <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テクスチャ</t>
+  </si>
+  <si>
+    <t>フレーム</t>
+  </si>
+  <si>
+    <t>スウォーム</t>
+  </si>
+  <si>
+    <t>en003</t>
+  </si>
+  <si>
+    <t>フライ</t>
+  </si>
+  <si>
+    <t>スピリット</t>
+  </si>
+  <si>
+    <t>マノウォー</t>
+  </si>
+  <si>
+    <t>ゴブリン</t>
+  </si>
+  <si>
+    <t>en001</t>
+  </si>
+  <si>
+    <t>コボルド</t>
+  </si>
+  <si>
+    <t>en002</t>
+  </si>
+  <si>
+    <t>オーク</t>
+  </si>
+  <si>
+    <t>オーガ</t>
+  </si>
+  <si>
+    <t>ゴーレム</t>
+  </si>
+  <si>
+    <t>ルームコード(x座標(0~4)+(floor*5))の値によって登場する2種類の雑魚が決まる</t>
+    <rPh sb="8" eb="10">
+      <t>ザヒョウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>トウジョウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ザコ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1編成目はRCを9で割った余り</t>
+    <rPh sb="1" eb="4">
+      <t>ヘンセイメ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>アマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2編成目はRCを8で割った余り</t>
+    <rPh sb="1" eb="4">
+      <t>ヘンセイメ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>アマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スウォーム2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フライ2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スピリット2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マノウォー2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゴブリン2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コボルド2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オーク2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オーガ2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゴーレム2</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -760,12 +983,40 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -774,7 +1025,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -837,6 +1088,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2103,7 +2360,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C330838-1509-4517-B74C-E85A6ACA858C}">
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultRowHeight="36" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="5" width="9" style="11"/>
@@ -3159,6 +3416,23 @@
       </c>
       <c r="G60"/>
     </row>
+    <row r="61" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="11">
+        <v>0</v>
+      </c>
+      <c r="B61" s="11">
+        <v>1</v>
+      </c>
+      <c r="C61" s="11">
+        <v>2</v>
+      </c>
+      <c r="D61" s="11">
+        <v>3</v>
+      </c>
+      <c r="E61" s="11">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3166,6 +3440,2009 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A2955AD-BE75-4102-9F56-068F093ACE7B}">
+  <dimension ref="A1:AE73"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A1" s="21"/>
+      <c r="B1" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="M1" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="O1" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="S1" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="T1" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="U1" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="V1" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="W1" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="X1" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y1" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z1" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA1" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB1" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC1" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD1" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE1" s="21" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A2" s="22">
+        <v>0</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="21">
+        <v>9</v>
+      </c>
+      <c r="D2" s="21">
+        <f>T2*20</f>
+        <v>1000</v>
+      </c>
+      <c r="E2" s="21">
+        <v>3</v>
+      </c>
+      <c r="F2" s="21">
+        <v>6</v>
+      </c>
+      <c r="G2" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="21">
+        <v>4</v>
+      </c>
+      <c r="I2" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="J2" s="21">
+        <v>1</v>
+      </c>
+      <c r="K2" s="21">
+        <v>5</v>
+      </c>
+      <c r="L2" s="21">
+        <v>0</v>
+      </c>
+      <c r="M2" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="N2" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="O2" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="22">
+        <v>0</v>
+      </c>
+      <c r="R2" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="S2" s="21">
+        <v>9</v>
+      </c>
+      <c r="T2" s="21">
+        <v>50</v>
+      </c>
+      <c r="U2" s="21">
+        <v>3</v>
+      </c>
+      <c r="V2" s="21">
+        <v>6</v>
+      </c>
+      <c r="W2" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="X2" s="21">
+        <v>4</v>
+      </c>
+      <c r="Y2" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="Z2" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="21">
+        <v>5</v>
+      </c>
+      <c r="AB2" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="AD2" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE2" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A3" s="21">
+        <v>1</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="21">
+        <v>4</v>
+      </c>
+      <c r="D3" s="21">
+        <f t="shared" ref="D3:D10" si="0">T3*20</f>
+        <v>2000</v>
+      </c>
+      <c r="E3" s="21">
+        <v>2.5</v>
+      </c>
+      <c r="F3" s="21">
+        <v>4.5</v>
+      </c>
+      <c r="G3" s="21">
+        <v>0.45</v>
+      </c>
+      <c r="H3" s="21">
+        <v>6</v>
+      </c>
+      <c r="I3" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="21">
+        <v>1</v>
+      </c>
+      <c r="K3" s="21">
+        <v>10</v>
+      </c>
+      <c r="L3" s="21">
+        <v>0</v>
+      </c>
+      <c r="M3" s="21">
+        <v>0.75</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="O3" s="21">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="21">
+        <v>1</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="S3" s="21">
+        <v>4</v>
+      </c>
+      <c r="T3" s="21">
+        <v>100</v>
+      </c>
+      <c r="U3" s="21">
+        <v>2.5</v>
+      </c>
+      <c r="V3" s="21">
+        <v>4.5</v>
+      </c>
+      <c r="W3" s="21">
+        <v>0.45</v>
+      </c>
+      <c r="X3" s="21">
+        <v>6</v>
+      </c>
+      <c r="Y3" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="Z3" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="21">
+        <v>10</v>
+      </c>
+      <c r="AB3" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="21">
+        <v>0.75</v>
+      </c>
+      <c r="AD3" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE3" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A4" s="21">
+        <v>2</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="21">
+        <v>8</v>
+      </c>
+      <c r="D4" s="21">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="E4" s="21">
+        <v>1.6</v>
+      </c>
+      <c r="F4" s="21">
+        <v>6</v>
+      </c>
+      <c r="G4" s="21">
+        <v>0.4</v>
+      </c>
+      <c r="H4" s="21">
+        <v>6</v>
+      </c>
+      <c r="I4" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="21">
+        <v>1</v>
+      </c>
+      <c r="K4" s="21">
+        <v>45</v>
+      </c>
+      <c r="L4" s="21">
+        <v>50</v>
+      </c>
+      <c r="M4" s="21">
+        <v>1</v>
+      </c>
+      <c r="N4" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="O4" s="21">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="21">
+        <v>2</v>
+      </c>
+      <c r="R4" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="S4" s="21">
+        <v>8</v>
+      </c>
+      <c r="T4" s="21">
+        <v>150</v>
+      </c>
+      <c r="U4" s="21">
+        <v>1.6</v>
+      </c>
+      <c r="V4" s="21">
+        <v>6</v>
+      </c>
+      <c r="W4" s="21">
+        <v>0.4</v>
+      </c>
+      <c r="X4" s="21">
+        <v>6</v>
+      </c>
+      <c r="Y4" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="Z4" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="21">
+        <v>45</v>
+      </c>
+      <c r="AB4" s="21">
+        <v>50</v>
+      </c>
+      <c r="AC4" s="21">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE4" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A5" s="21">
+        <v>3</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="21">
+        <v>3</v>
+      </c>
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="E5" s="21">
+        <v>1</v>
+      </c>
+      <c r="F5" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="H5" s="21">
+        <v>8</v>
+      </c>
+      <c r="I5" s="21">
+        <v>1</v>
+      </c>
+      <c r="J5" s="21">
+        <v>1</v>
+      </c>
+      <c r="K5" s="21">
+        <v>15</v>
+      </c>
+      <c r="L5" s="21">
+        <v>50</v>
+      </c>
+      <c r="M5" s="21">
+        <v>1</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="O5" s="21">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="21">
+        <v>3</v>
+      </c>
+      <c r="R5" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="S5" s="21">
+        <v>3</v>
+      </c>
+      <c r="T5" s="21">
+        <v>200</v>
+      </c>
+      <c r="U5" s="21">
+        <v>1</v>
+      </c>
+      <c r="V5" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="W5" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="X5" s="21">
+        <v>8</v>
+      </c>
+      <c r="Y5" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="21">
+        <v>15</v>
+      </c>
+      <c r="AB5" s="21">
+        <v>50</v>
+      </c>
+      <c r="AC5" s="21">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE5" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A6" s="21">
+        <v>4</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="21">
+        <v>8</v>
+      </c>
+      <c r="D6" s="21">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="E6" s="21">
+        <v>10</v>
+      </c>
+      <c r="F6" s="21">
+        <v>0.8</v>
+      </c>
+      <c r="G6" s="21">
+        <v>0.25</v>
+      </c>
+      <c r="H6" s="21">
+        <v>4</v>
+      </c>
+      <c r="I6" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="J6" s="21">
+        <v>1</v>
+      </c>
+      <c r="K6" s="21">
+        <v>35</v>
+      </c>
+      <c r="L6" s="21">
+        <v>0</v>
+      </c>
+      <c r="M6" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="N6" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="O6" s="21">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="21">
+        <v>4</v>
+      </c>
+      <c r="R6" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="S6" s="21">
+        <v>8</v>
+      </c>
+      <c r="T6" s="21">
+        <v>200</v>
+      </c>
+      <c r="U6" s="21">
+        <v>10</v>
+      </c>
+      <c r="V6" s="21">
+        <v>0.8</v>
+      </c>
+      <c r="W6" s="21">
+        <v>0.25</v>
+      </c>
+      <c r="X6" s="21">
+        <v>4</v>
+      </c>
+      <c r="Y6" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="Z6" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="21">
+        <v>35</v>
+      </c>
+      <c r="AB6" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="AD6" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AE6" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A7" s="21">
+        <v>5</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="21">
+        <v>6</v>
+      </c>
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
+      <c r="E7" s="21">
+        <v>8</v>
+      </c>
+      <c r="F7" s="21">
+        <v>1</v>
+      </c>
+      <c r="G7" s="21">
+        <v>0.35</v>
+      </c>
+      <c r="H7" s="21">
+        <v>6</v>
+      </c>
+      <c r="I7" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="J7" s="21">
+        <v>1</v>
+      </c>
+      <c r="K7" s="21">
+        <v>55</v>
+      </c>
+      <c r="L7" s="21">
+        <v>50</v>
+      </c>
+      <c r="M7" s="21">
+        <v>0.75</v>
+      </c>
+      <c r="N7" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="O7" s="21">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="21">
+        <v>5</v>
+      </c>
+      <c r="R7" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="S7" s="21">
+        <v>6</v>
+      </c>
+      <c r="T7" s="21">
+        <v>250</v>
+      </c>
+      <c r="U7" s="21">
+        <v>8</v>
+      </c>
+      <c r="V7" s="21">
+        <v>1</v>
+      </c>
+      <c r="W7" s="21">
+        <v>0.35</v>
+      </c>
+      <c r="X7" s="21">
+        <v>6</v>
+      </c>
+      <c r="Y7" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="Z7" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="21">
+        <v>55</v>
+      </c>
+      <c r="AB7" s="21">
+        <v>50</v>
+      </c>
+      <c r="AC7" s="21">
+        <v>0.75</v>
+      </c>
+      <c r="AD7" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE7" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A8" s="21">
+        <v>6</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="21">
+        <v>6</v>
+      </c>
+      <c r="D8" s="21">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="E8" s="21">
+        <v>7</v>
+      </c>
+      <c r="F8" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="G8" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="21">
+        <v>8</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="J8" s="21">
+        <v>1</v>
+      </c>
+      <c r="K8" s="21">
+        <v>75</v>
+      </c>
+      <c r="L8" s="21">
+        <v>0</v>
+      </c>
+      <c r="M8" s="21">
+        <v>0.75</v>
+      </c>
+      <c r="N8" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="O8" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="21">
+        <v>6</v>
+      </c>
+      <c r="R8" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="S8" s="21">
+        <v>6</v>
+      </c>
+      <c r="T8" s="21">
+        <v>300</v>
+      </c>
+      <c r="U8" s="21">
+        <v>7</v>
+      </c>
+      <c r="V8" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="W8" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="X8" s="21">
+        <v>8</v>
+      </c>
+      <c r="Y8" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="Z8" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="21">
+        <v>75</v>
+      </c>
+      <c r="AB8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="21">
+        <v>0.75</v>
+      </c>
+      <c r="AD8" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AE8" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A9" s="21">
+        <v>7</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="21">
+        <v>3</v>
+      </c>
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
+      <c r="E9" s="21">
+        <v>6</v>
+      </c>
+      <c r="F9" s="21">
+        <v>1.25</v>
+      </c>
+      <c r="G9" s="21">
+        <v>0.35</v>
+      </c>
+      <c r="H9" s="21">
+        <v>8</v>
+      </c>
+      <c r="I9" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="J9" s="21">
+        <v>1</v>
+      </c>
+      <c r="K9" s="21">
+        <v>110</v>
+      </c>
+      <c r="L9" s="21">
+        <v>50</v>
+      </c>
+      <c r="M9" s="21">
+        <v>1</v>
+      </c>
+      <c r="N9" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="O9" s="21">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="21">
+        <v>7</v>
+      </c>
+      <c r="R9" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="S9" s="21">
+        <v>3</v>
+      </c>
+      <c r="T9" s="21">
+        <v>400</v>
+      </c>
+      <c r="U9" s="21">
+        <v>6</v>
+      </c>
+      <c r="V9" s="21">
+        <v>1.25</v>
+      </c>
+      <c r="W9" s="21">
+        <v>0.35</v>
+      </c>
+      <c r="X9" s="21">
+        <v>8</v>
+      </c>
+      <c r="Y9" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="Z9" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="21">
+        <v>110</v>
+      </c>
+      <c r="AB9" s="21">
+        <v>50</v>
+      </c>
+      <c r="AC9" s="21">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE9" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A10" s="21">
+        <v>8</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="21">
+        <v>1</v>
+      </c>
+      <c r="D10" s="21">
+        <f t="shared" si="0"/>
+        <v>20000</v>
+      </c>
+      <c r="E10" s="21">
+        <v>2</v>
+      </c>
+      <c r="F10" s="21">
+        <v>3.6</v>
+      </c>
+      <c r="G10" s="21">
+        <v>0.6</v>
+      </c>
+      <c r="H10" s="21">
+        <v>4</v>
+      </c>
+      <c r="I10" s="21">
+        <v>1</v>
+      </c>
+      <c r="J10" s="21">
+        <v>1</v>
+      </c>
+      <c r="K10" s="21">
+        <v>110</v>
+      </c>
+      <c r="L10" s="21">
+        <v>50</v>
+      </c>
+      <c r="M10" s="21">
+        <v>1.25</v>
+      </c>
+      <c r="N10" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="O10" s="21">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="21">
+        <v>8</v>
+      </c>
+      <c r="R10" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="S10" s="21">
+        <v>1</v>
+      </c>
+      <c r="T10" s="21">
+        <v>1000</v>
+      </c>
+      <c r="U10" s="21">
+        <v>2</v>
+      </c>
+      <c r="V10" s="21">
+        <v>3.6</v>
+      </c>
+      <c r="W10" s="21">
+        <v>0.6</v>
+      </c>
+      <c r="X10" s="21">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="21">
+        <v>110</v>
+      </c>
+      <c r="AB10" s="21">
+        <v>50</v>
+      </c>
+      <c r="AC10" s="21">
+        <v>1.25</v>
+      </c>
+      <c r="AD10" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE10" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="H14" t="s">
+        <v>141</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <f>MOD(K14,9)</f>
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <f>MOD(K14+3,8)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15">
+        <f>B$14+$A15*5</f>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:F25" si="1">C$14+$A15*5</f>
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="H15" t="s">
+        <v>142</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <f>MOD(K15,9)</f>
+        <v>2</v>
+      </c>
+      <c r="M15">
+        <f t="shared" ref="M15:M43" si="2">MOD(K15+3,8)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <f>B$14+$A16*5</f>
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="K16">
+        <v>3</v>
+      </c>
+      <c r="L16">
+        <f t="shared" ref="L16:L75" si="3">MOD(K16,9)</f>
+        <v>3</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <f t="shared" ref="B17:B25" si="4">B$14+$A17*5</f>
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="K17">
+        <v>4</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="K18">
+        <v>5</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>4</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="K19">
+        <v>6</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="K20">
+        <v>7</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>6</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="K21">
+        <v>8</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>7</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="K22">
+        <v>9</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>8</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="K23">
+        <v>10</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>9</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="K24">
+        <v>11</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>10</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="K25">
+        <v>12</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="K26">
+        <v>13</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="K27">
+        <v>14</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="K28">
+        <v>15</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="K29">
+        <v>16</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="K30">
+        <v>17</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="K31">
+        <v>18</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="K32">
+        <v>19</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K33">
+        <v>20</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K34">
+        <v>21</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K35">
+        <v>22</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K36">
+        <v>23</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K37">
+        <v>24</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K38">
+        <v>25</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K39">
+        <v>26</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K40">
+        <v>27</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K41">
+        <v>28</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K42">
+        <v>29</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K43">
+        <v>30</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K44">
+        <v>31</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="M44">
+        <f t="shared" ref="M44:M75" si="5">MOD(K44+3,8)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K45">
+        <v>32</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K46">
+        <v>33</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K47">
+        <v>34</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K48">
+        <v>35</v>
+      </c>
+      <c r="L48">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K49">
+        <v>36</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K50">
+        <v>37</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K51">
+        <v>38</v>
+      </c>
+      <c r="L51">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K52">
+        <v>39</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="M52">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K53">
+        <v>40</v>
+      </c>
+      <c r="L53">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="M53">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K54">
+        <v>41</v>
+      </c>
+      <c r="L54">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="M54">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K55">
+        <v>42</v>
+      </c>
+      <c r="L55">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="M55">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K56">
+        <v>43</v>
+      </c>
+      <c r="L56">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="M56">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K57">
+        <v>44</v>
+      </c>
+      <c r="L57">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="M57">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K58">
+        <v>45</v>
+      </c>
+      <c r="L58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K59">
+        <v>46</v>
+      </c>
+      <c r="L59">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="M59">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K60">
+        <v>47</v>
+      </c>
+      <c r="L60">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="M60">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K61">
+        <v>48</v>
+      </c>
+      <c r="L61">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="M61">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K62">
+        <v>49</v>
+      </c>
+      <c r="L62">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="M62">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K63">
+        <v>50</v>
+      </c>
+      <c r="L63">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="M63">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K64">
+        <v>51</v>
+      </c>
+      <c r="L64">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="M64">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K65">
+        <v>52</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="M65">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K66">
+        <v>53</v>
+      </c>
+      <c r="L66">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="M66">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K67">
+        <v>54</v>
+      </c>
+      <c r="L67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K68">
+        <v>55</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="M68">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K69">
+        <v>56</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="M69">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K70">
+        <v>57</v>
+      </c>
+      <c r="L70">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="M70">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K71">
+        <v>58</v>
+      </c>
+      <c r="L71">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="M71">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K72">
+        <v>59</v>
+      </c>
+      <c r="L72">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="M72">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="11:13" x14ac:dyDescent="0.4">
+      <c r="K73">
+        <v>60</v>
+      </c>
+      <c r="L73">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="M73">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35C49FFA-D35B-4AF1-B8C1-B7B935FDDD03}">
   <dimension ref="A1:O60"/>
   <sheetFormatPr defaultColWidth="4.5" defaultRowHeight="36" customHeight="1" x14ac:dyDescent="0.4"/>
